--- a/ебанаты (кроме кисули).xlsx
+++ b/ебанаты (кроме кисули).xlsx
@@ -14,9 +14,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="16">
-  <si>
-    <t>Екатерина Тимофеева</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="26">
+  <si>
+    <t>03-03-2026</t>
+  </si>
+  <si>
+    <t>05-03-2026</t>
+  </si>
+  <si>
+    <t>06-03-2026</t>
   </si>
   <si>
     <t>Вероника Второва</t>
@@ -28,49 +34,70 @@
     <t>Анфиса Солодянкина</t>
   </si>
   <si>
+    <t>Безруков Артём</t>
+  </si>
+  <si>
+    <t>Динара Акшова</t>
+  </si>
+  <si>
+    <t>Дмитрий Фадеев</t>
+  </si>
+  <si>
+    <t>Евгений Гаврилов</t>
+  </si>
+  <si>
+    <t>Екатерина Синотагина</t>
+  </si>
+  <si>
+    <t>Ирина Тюрина</t>
+  </si>
+  <si>
+    <t>Кирилл Кочергин</t>
+  </si>
+  <si>
+    <t>Ксения Тюряпина</t>
+  </si>
+  <si>
+    <t>Надежда Хохлова</t>
+  </si>
+  <si>
+    <t>Полина Агафонова</t>
+  </si>
+  <si>
+    <t>Сергей Батуев</t>
+  </si>
+  <si>
+    <t>Федор Науменко</t>
+  </si>
+  <si>
+    <t>Екатерина Киселева</t>
+  </si>
+  <si>
+    <t>Ирина Ушакова</t>
+  </si>
+  <si>
+    <t>Калистратова Наталья</t>
+  </si>
+  <si>
+    <t>Кузьмина Виктория</t>
+  </si>
+  <si>
+    <t>Мадина Задворочнова</t>
+  </si>
+  <si>
+    <t>Астахина Юлия</t>
+  </si>
+  <si>
     <t>Безруков Артём Романович</t>
   </si>
   <si>
-    <t>Динара Акшова</t>
-  </si>
-  <si>
-    <t>Дмитрий Фадеев</t>
-  </si>
-  <si>
-    <t>Евгений Гаврилов</t>
-  </si>
-  <si>
-    <t>Екатерина Синотагина</t>
-  </si>
-  <si>
-    <t>Ирина Тюрина</t>
-  </si>
-  <si>
-    <t>Кирилл Кочергин</t>
-  </si>
-  <si>
-    <t>Ксения Тюряпина</t>
-  </si>
-  <si>
-    <t>Надежда Хохлова</t>
-  </si>
-  <si>
-    <t>Полина Агафонова</t>
-  </si>
-  <si>
-    <t>Сергей Батуев</t>
-  </si>
-  <si>
-    <t>Федор Науменко</t>
+    <t>Яна Ситдикова</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
-  </numFmts>
   <fonts count="1">
     <font>
       <sz val="11"/>
@@ -100,9 +127,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -397,128 +423,196 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" s="1">
-        <v>46084</v>
-      </c>
-      <c r="B1" s="1">
-        <v>46145</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
+    <row r="1" spans="1:3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
-      <c r="A4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" t="s">
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
-      <c r="A6" t="s">
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" t="s">
         <v>4</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3">
+      <c r="B17" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
-      <c r="A9" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
-      <c r="A10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
-      <c r="A11" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
-      <c r="A12" t="s">
-        <v>10</v>
-      </c>
-      <c r="B12" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
-      <c r="A13" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
-      <c r="A14" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
-      <c r="A15" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2">
-      <c r="A16" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" t="s">
-        <v>15</v>
+      <c r="C17" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3">
+      <c r="C18" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
